--- a/03-Tasks/translation_template.xlsx
+++ b/03-Tasks/translation_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erinbuchanan/GitHub/Research/2_projects/ManyLanguages-Grant/ML-One-Network/03-Tasks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/addieclark/Desktop/Harrisburg/SPAML/ML-One-Network/03-Tasks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50B1CA8F-3CAA-764C-88A6-3D171635AE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21142FC-8269-FE4E-A72A-496398506125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="18740" xr2:uid="{C0956B13-467A-1A4F-848B-48D89FEF3597}"/>
+    <workbookView xWindow="17180" yWindow="760" windowWidth="17520" windowHeight="21580" xr2:uid="{C0956B13-467A-1A4F-848B-48D89FEF3597}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,26 +35,602 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={2987ABC4-BFFE-D241-A1E9-00D4B209872D}</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{2987ABC4-BFFE-D241-A1E9-00D4B209872D}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    don't forget text for buttons e.g.,         
+completeText: "Finish",
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
-  <si>
-    <t>Age of Acquisition Study</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Thank you&lt;/h2&gt;&lt;p&gt;You have chosen not to participate. You may close this window.&lt;/p&gt;</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="134">
   <si>
     <t>aoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age of Acquisition Study </t>
+  </si>
+  <si>
+    <t>&lt;title&gt;Age of Acquisition Study&lt;/title&gt;</t>
+  </si>
+  <si>
+    <t>Thank you You have chosen not to participate. You may close this window.</t>
+  </si>
+  <si>
+    <t>pageNextText: "Next",</t>
+  </si>
+  <si>
+    <t>pagePrevText: "Back",</t>
+  </si>
+  <si>
+    <t>completeText: "Next",</t>
+  </si>
+  <si>
+    <t>Next</t>
+  </si>
+  <si>
+    <t>Back</t>
+  </si>
+  <si>
+    <t>title: "Consent to Participate",</t>
+  </si>
+  <si>
+    <t>Consent to Participate</t>
+  </si>
+  <si>
+    <t>Please read the following carefully before continuing:
+This study involves completing brief questions and/or tasks about language and cognition. Your participation is voluntary. You may stop at any time without penalty. Your responses will be recorded for research purposes but will be kept confidential and analyzed in anonymized form.
+By proceeding you indicate that you are at least 18 years old.</t>
+  </si>
+  <si>
+    <t>title: "Do you consent to participate?"</t>
+  </si>
+  <si>
+    <t>Do you consent to participate?</t>
+  </si>
+  <si>
+    <t>choices: ["I Consent", "I Do Not Consent"]</t>
+  </si>
+  <si>
+    <t>"I Consent", "I Do Not Consent"</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> choices: ["Close"]</t>
+  </si>
+  <si>
+    <t>93-96</t>
+  </si>
+  <si>
+    <t>title: "Demographic Information"</t>
+  </si>
+  <si>
+    <t>Demographic Information</t>
+  </si>
+  <si>
+    <t>title: "Please tell us your gender:",</t>
+  </si>
+  <si>
+    <t>Please tell us your gender:</t>
+  </si>
+  <si>
+    <t>choices: ["Male", "Female", "Other", "Prefer not to say"],</t>
+  </si>
+  <si>
+    <t>"Male", "Female", "Other", "Prefer not to say"</t>
+  </si>
+  <si>
+    <t>title: "Which year were you born? Please enter a four-digit year",</t>
+  </si>
+  <si>
+    <t>Which year were you born? Please enter a four-digit year</t>
+  </si>
+  <si>
+    <t>title: "Please tell us your highest education level:"</t>
+  </si>
+  <si>
+    <t>Please tell us your highest education level:</t>
+  </si>
+  <si>
+    <t>choices: [
+                "Less than high school diploma",
+                "High school diploma",
+                "Associate's degree or two-year degree",
+                "Bachelor's degree or four-year degree",
+                "Master's degree or equivalent",
+                "Doctoral degree or equivalent",
+              ]</t>
+  </si>
+  <si>
+    <t>133-140</t>
+  </si>
+  <si>
+    <t>"Less than high school diploma", "High school diploma", "Associate's degree or two-year degree", "Bachelor's degree or four-year degree", "Master's degree or equivalent", "Doctoral degree or equivalent"</t>
+  </si>
+  <si>
+    <t>title: "What is your native (first) language?",</t>
+  </si>
+  <si>
+    <t>What is your native (first) language?</t>
+  </si>
+  <si>
+    <t>Are you primarily left- or right-handed?</t>
+  </si>
+  <si>
+    <t>title: "Are you primarily left- or right-handed?",</t>
+  </si>
+  <si>
+    <t>choices: ["Left-handed", "Right-handed"],</t>
+  </si>
+  <si>
+    <t>"Left-handed", "Right-handed"</t>
+  </si>
+  <si>
+    <t>166-170</t>
+  </si>
+  <si>
+    <t>Please rate the following words by entering the age in years at which you think you learned the word.
+We mean the age at which you would have understood the word if somebody had used it in front of you, EVEN IF YOU DID NOT use, read, or write it at the time.
+If you do not know the word, please enter the letter X.
+              `</t>
+  </si>
+  <si>
+    <t>html: `
+                &lt;p&gt;Please read the following carefully before continuing:&lt;/p&gt;
+                &lt;p&gt;This study involves completing brief questions and/or tasks about language and cognition. Your participation is voluntary. You may stop at any time without penalty. Your responses will be recorded for research purposes but will be kept confidential and analyzed in anonymized form.&lt;/p&gt;
+                &lt;p&gt;By proceeding you indicate that you are at least 18 years old.&lt;/p&gt;
+              `</t>
+  </si>
+  <si>
+    <t>html: `
+                &lt;p&gt;Please rate the following words by entering the age in years at which you think you learned the word.&lt;/p&gt;
+                &lt;p&gt;We mean the age at which you would have understood the word if somebody had used it in front of you, &lt;strong&gt;EVEN IF YOU DID NOT&lt;/strong&gt; use, read, or write it at the time.&lt;/p&gt;
+                &lt;p&gt;If you do &lt;strong&gt;not know&lt;/strong&gt; the word, please enter the letter &lt;strong&gt;X&lt;/strong&gt;.&lt;/p&gt;
+              `</t>
+  </si>
+  <si>
+    <t>const sampleWords = [
+      "dog",
+      "bicycle",
+      "apple",
+      "school",
+      "mountain",
+      "telephone",
+      "democracy",
+      "hospital",
+      "garden",
+      "computer",
+      "river",
+      "window",
+    ]</t>
+  </si>
+  <si>
+    <t>"dog", "bicycle", "apple", "school", "mountain", "telephone", "democracy", "hospital", "garden", "computer", "river", "window"</t>
+  </si>
+  <si>
+    <t>186-199</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> completeText: "Next",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title:
+                  "For each word, enter the age (in years) when you think you learned it, or X if unknown.",
+               </t>
+  </si>
+  <si>
+    <t>226-227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each word, enter the age (in years) when you think you learned it, or X if unknown.
+               </t>
+  </si>
+  <si>
+    <t>text: "Enter a number between 1 and 100, or X if unknown",</t>
+  </si>
+  <si>
+    <t>Enter a number between 1 and 100, or X if unknown</t>
+  </si>
+  <si>
+    <t>completeText: "Finish",</t>
+  </si>
+  <si>
+    <t>Finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> title: "Thank you for participating",</t>
+  </si>
+  <si>
+    <t>Thank you for participating</t>
+  </si>
+  <si>
+    <t>276-281</t>
+  </si>
+  <si>
+    <t>html: `
+                  &lt;p&gt;You have completed the word ratings.&lt;/p&gt;
+                  &lt;p&gt;Your participant number is:&lt;/p&gt;
+                  &lt;p&gt;&lt;strong&gt;${participant_uuid}&lt;/strong&gt;&lt;/p&gt;
+                  &lt;p&gt;Please keep or copy this number if you are asked for it.&lt;/p&gt;
+                `</t>
+  </si>
+  <si>
+    <t>You have completed the word ratings.
+Your participant number is:
+${participant_uuid}
+Please keep or copy this number if you are asked for it.
+                `</t>
+  </si>
+  <si>
+    <t>return last.consent_choice === "I Do Not Consent";</t>
+  </si>
+  <si>
+    <t>return last.consent_choice === "I Do Not Consent"</t>
+  </si>
+  <si>
+    <t>stimulus: &lt;h2&gt;Thank you&lt;/h2&gt;&lt;p&gt;You have chosen not to participate. You may close this window.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>concrete</t>
+  </si>
+  <si>
+    <t>&lt;title&gt;Concreteness Study&lt;/title&gt;</t>
+  </si>
+  <si>
+    <t>Concreteness Study</t>
+  </si>
+  <si>
+    <t>93-97</t>
+  </si>
+  <si>
+    <t>visibleIf: "{consent_choice} = 'I Consent'",</t>
+  </si>
+  <si>
+    <t>visibleIf: "{consent_choice} = 'I Consent'"</t>
+  </si>
+  <si>
+    <t>title: "How to do this task",</t>
+  </si>
+  <si>
+    <t>How to do this task</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> visibleIf: "{consent_choice} = 'I Consent'"</t>
+  </si>
+  <si>
+    <t>166-172</t>
+  </si>
+  <si>
+    <t>html: `
+                &lt;p&gt;Some words refer to things or actions in reality, which you can experience directly through one of the five senses. We call these words concrete words. Other words refer to meanings that cannot be experienced directly but which we know because the meanings can be defined by other words. These are abstract words. Still other words fall in-between the two extremes, because we can experience them to some extent and in addition we rely on language to understand them. &lt;/p&gt;
+                &lt;p&gt;We want you to indicate how concrete the meaning of each word is for you by using a 9-point rating scale going from abstract to concrete. A concrete word comes with a higher rating and refers to something that exists in reality; you can have immediate experience of it through your senses (smelling, tasting, touching, hearing, seeing) and the actions you do. The easiest way to explain a word is by pointing to it or by demonstrating it (e.g. To explain 'sweet' you could have someone eat sugar; To explain 'jump' you could simply jump up and down or show people a movie clip about someone jumping up and down; To explain 'couch', you could point to a couch or show a picture of a couch). &lt;/p&gt;
+                &lt;p&gt;An abstract word comes with a lower rating and refers to something you cannot experience directly through your senses or actions. Its meaning depends on language. The easiest way to explain it is by using other words (e.g. There is no simple way to demonstrate 'justice'; but we can explain the meaning of the word by using other words that capture parts of its meaning).&lt;/p&gt;
+                &lt;p&gt;Because we are collecting values for all the words in a dictionary (over 60 thousand in total), you will see that there are various types of words, even single letters. Always think of how concrete (experience based) the meaning of the word is to you. In all likelihood, you will encounter several words you do not know well enough to give a useful rating. This is informative to us too, as in our research we only want to use words known to people. We may also include one or two fake words which cannot be known by you. Please indicate when you don't know a word by using the letter X (or x).Because we are collecting values for all the words in a dictionary (over 60 thousand in total), you will see that there are various types of words, even single letters. Always think of how concrete (experience based) the meaning of the word is to you. In all likelihood, you will encounter several words you do not know well enough to give a useful rating. This is informative to us too, as in our research we only want to use words known to people. We may also include one or two fake words which cannot be known by you. Please indicate when you don't know a word by using the letter X (or x).&lt;/p&gt;
+                &lt;p&gt;For each word, rate how abstract (1) or concrete (9) based on your first impression of the object and entering 'X' when you do not know a word.&lt;/p&gt;
+              `</t>
+  </si>
+  <si>
+    <t>Some words refer to things or actions in reality, which you can experience directly through one of the five senses. We call these words concrete words. Other words refer to meanings that cannot be experienced directly but which we know because the meanings can be defined by other words. These are abstract words. Still other words fall in-between the two extremes, because we can experience them to some extent and in addition we rely on language to understand them.
+We want you to indicate how concrete the meaning of each word is for you by using a 9-point rating scale going from abstract to concrete. A concrete word comes with a higher rating and refers to something that exists in reality; you can have immediate experience of it through your senses (smelling, tasting, touching, hearing, seeing) and the actions you do. The easiest way to explain a word is by pointing to it or by demonstrating it (e.g. To explain 'sweet' you could have someone eat sugar; To explain 'jump' you could simply jump up and down or show people a movie clip about someone jumping up and down; To explain 'couch', you could point to a couch or show a picture of a couch). 
+An abstract word comes with a lower rating and refers to something you cannot experience directly through your senses or actions. Its meaning depends on language. The easiest way to explain it is by using other words (e.g. There is no simple way to demonstrate 'justice'; but we can explain the meaning of the word by using other words that capture parts of its meaning).
+Because we are collecting values for all the words in a dictionary (over 60 thousand in total), you will see that there are various types of words, even single letters. Always think of how concrete (experience based) the meaning of the word is to you. In all likelihood, you will encounter several words you do not know well enough to give a useful rating. This is informative to us too, as in our research we only want to use words known to people. We may also include one or two fake words which cannot be known by you. Please indicate when you don't know a word by using the letter X (or x).Because we are collecting values for all the words in a dictionary (over 60 thousand in total), you will see that there are various types of words, even single letters. Always think of how concrete (experience based) the meaning of the word is to you. In all likelihood, you will encounter several words you do not know well enough to give a useful rating. This is informative to us too, as in our research we only want to use words known to people. We may also include one or two fake words which cannot be known by you. Please indicate when you don't know a word by using the letter X (or x).
+For each word, rate how abstract (1) or concrete (9) based on your first impression of the object and entering 'X' when you do not know a word.</t>
+  </si>
+  <si>
+    <t>188-201</t>
+  </si>
+  <si>
+    <t>title: `Word ratings (Block ${blockIndex + 1} of ${wordBlocks.length})`,</t>
+  </si>
+  <si>
+    <t>Word ratings (Block ${blockIndex + 1} of ${wordBlocks.length})</t>
+  </si>
+  <si>
+    <t>228-229</t>
+  </si>
+  <si>
+    <t>title:
+                  "For each word, rate how abstract (1) or concrete (9) based on your first impression of the object and entering 'X' when you do not know a word.",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each word, rate how abstract (1) or concrete (9) based on your first impression of the object and entering 'X' when you do not know a word.
+                </t>
+  </si>
+  <si>
+    <t>text: "Enter a number between 1 and 9",</t>
+  </si>
+  <si>
+    <t>Enter a number between 1 and 9</t>
+  </si>
+  <si>
+    <t>278-283</t>
+  </si>
+  <si>
+    <t>&lt;title&gt;Valence Study&lt;/title&gt;</t>
+  </si>
+  <si>
+    <t>Valence Study</t>
+  </si>
+  <si>
+    <t>valence</t>
+  </si>
+  <si>
+    <t>95-99</t>
+  </si>
+  <si>
+    <t>135-142</t>
+  </si>
+  <si>
+    <t>html: `
+                &lt;figure style="margin: 0 0 1rem 0;"&gt;
+                  &lt;img
+                    src="valence_image.png"
+                    alt="Self-Assessment Manikin (SAM) scale for valence"
+                    style="max-width: 100%; height: auto; display: block;"
+                  /&gt;
+                  &lt;figcaption style="font-size: 0.9em; margin-top: 0.25rem;"&gt;
+                    &lt;em&gt;Self-Assessment Manikin (SAM)&lt;/em&gt; valence scale. Procedure adapted from Prete, Laeng, &amp;amp; Tommasi (2022); SAM from Bradley &amp;amp; Lang (1999).
+                   &lt;/figcaption&gt;
+                &lt;/figure&gt;
+                &lt;p&gt;The study being conducted today is investigating emotion, and how people respond to different types of words.&lt;/p&gt;
+                &lt;p&gt;We call this set of figures SAM, and you will be using these figures to rate how you felt while reading each word. SAM shows different kinds of feelings: Happy vs. Unhappy and  Excited vs. Calm. You will use these scales to make all ratings for each word that you read. Please notice that each of the feelings are arrayed along a different scale. &lt;/p&gt;
+                &lt;p&gt;The top panel shows the happy-unhappy scale, which ranges from a frown to a smile. At one extreme of this scale, you are happy, pleased, satisfied, contented, hopeful. When you feel completely happy you should indicate this by selecting the 9 on the right. The other end of the scale is when you feel completely unhappy, annoyed, unsatisfied, melancholic, despaired, or bored. You can indicate feeling completely unhappy by selecting the 1 on the left. The figures also allow you to describe intermediate feelings of pleasure, by selecting any values in the middle. If you feel completely neutral, neither happy nor sad, select the 4 in the middle. &lt;/p&gt;
+                &lt;p&gt;Please work at a rapid place and don’t spend too much time thinking about each word. Rather, make your ratings based on your first and immediate reaction as you read each word.&lt;/p&gt;
+              `</t>
+  </si>
+  <si>
+    <t>168-184</t>
+  </si>
+  <si>
+    <t>Self-Assessment Manikin (SAM) scale for valence
+Self-Assessment Manikin (SAM) valence scale. Procedure adapted from Prete, Laeng, &amp;amp; Tommasi (2022); SAM from Bradley &amp;amp; Lang (1999).
+The study being conducted today is investigating emotion, and how people respond to different types of words.
+We call this set of figures SAM, and you will be using these figures to rate how you felt while reading each word. SAM shows different kinds of feelings: Happy vs. Unhappy and  Excited vs. Calm. You will use these scales to make all ratings for each word that you read. Please notice that each of the feelings are arrayed along a different scale.
+The top panel shows the happy-unhappy scale, which ranges from a frown to a smile. At one extreme of this scale, you are happy, pleased, satisfied, contented, hopeful. When you feel completely happy you should indicate this by selecting the 9 on the right. The other end of the scale is when you feel completely unhappy, annoyed, unsatisfied, melancholic, despaired, or bored. You can indicate feeling completely unhappy by selecting the 1 on the left. The figures also allow you to describe intermediate feelings of pleasure, by selecting any values in the middle. If you feel completely neutral, neither happy nor sad, select the 4 in the middle. 
+Please work at a rapid place and don’t spend too much time thinking about each word. Rather, make your ratings based on your first and immediate reaction as you read each word.</t>
+  </si>
+  <si>
+    <t>200-213</t>
+  </si>
+  <si>
+    <t>const samHtml = `
+        &lt;figure style="margin: 0 0 1rem 0;"&gt;
+          &lt;img
+            src="valence_image.png"
+            alt="Self-Assessment Manikin (SAM) scale for valence"
+            style="max-width: 100%; height: auto; display: block;"
+          /&gt;
+          &lt;figcaption style="font-size: 0.9em; margin-top: 0.25rem;"&gt;
+            &lt;em&gt;Self-Assessment Manikin (SAM)&lt;/em&gt; valence scale. Procedure adapted from Prete, Laeng, &amp;amp; Tommasi (2022); SAM from Bradley &amp;amp; Lang (1999).
+          &lt;/figcaption&gt;
+        &lt;/figure&gt;
+      `</t>
+  </si>
+  <si>
+    <t>227-238</t>
+  </si>
+  <si>
+    <t>title: `Valence ratings (Block ${blockIndex + 1} of ${wordBlocks.length})`,</t>
+  </si>
+  <si>
+    <t>Valence ratings (Block ${blockIndex + 1} of ${wordBlocks.length})</t>
+  </si>
+  <si>
+    <t>258-259</t>
+  </si>
+  <si>
+    <t>title:
+                "For each word, rate VALENCE (1 = very unpleasant/unhappy, 9 = very pleasant/happy). If you do not know the word, choose X.",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each word, rate VALENCE (1 = very unpleasant/unhappy, 9 = very pleasant/happy). If you do not know the word, choose X.
+             </t>
+  </si>
+  <si>
+    <t>296-301</t>
+  </si>
+  <si>
+    <t>return last.response &amp;&amp; last.response.consent_choice === "I Consent";</t>
+  </si>
+  <si>
+    <t>return last.response &amp;&amp; last.response.consent_choice === "I Consent"</t>
+  </si>
+  <si>
+    <t>return last.response &amp;&amp; last.response.consent_choice === "I Do Not Consent";</t>
+  </si>
+  <si>
+    <t>return last.response &amp;&amp; last.response.consent_choice === "I Do Not Consent"</t>
+  </si>
+  <si>
+    <t>&lt;title&gt;Imageability Study&lt;/title&gt;</t>
+  </si>
+  <si>
+    <t>Imageability Study</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>html: `
+                &lt;p&gt;This is an experiment to find out how easy or difficult it is to imagine a mental picture of the word presented to you. You will be given a list of words and you are to rate each one from how easy it is to picture the word (apple; high imagery) to words that may not be imagined easily (fact; low imagery).&lt;/p&gt; 
+                &lt;p&gt;In this scale, 9 represents “easy to imagine,” there is no issue picturing intricate details of the word; while 1 represents “difficult to image,” that is, the word is more abstract and harder to picture.&lt;/p&gt; 
+                &lt;p&gt;If you do not know the word presented, please enter “X”. &lt;/p&gt;
+              `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is an experiment to find out how easy or difficult it is to imagine a mental picture of the word presented to you. You will be given a list of words and you are to rate each one from how easy it is to picture the word (apple; high imagery) to words that may not be imagined easily (fact; low imagery).
+In this scale, 9 represents “easy to imagine,” there is no issue picturing intricate details of the word; while 1 represents “difficult to image,” that is, the word is more abstract and harder to picture.
+If you do not know the word presented, please enter “X”. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">title:
+                  "For each word, rate how difficult (1) or easy (9) it is to imagine a mental picture of the object.",
+               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each word, rate how difficult (1) or easy (9) it is to imagine a mental picture of the object.
+               </t>
+  </si>
+  <si>
+    <t>&lt;title&gt;Familiarity Study&lt;/title&gt;</t>
+  </si>
+  <si>
+    <t>Familiarity Study</t>
+  </si>
+  <si>
+    <t>familiar</t>
+  </si>
+  <si>
+    <t>166-171</t>
+  </si>
+  <si>
+    <t>html: `
+                &lt;p&gt;This is an experiment to find out how often you have come in contact with certain words. You will be given a list of words and you are to rate each one as to the number of times that you experienced it by simply writing down a number according to a 1 to 9 scale. In this scale, 1 represents “NEVER,” that is, you have never seen or heard or used the word in your life; the number 2 represents “RARELY,” that is you have seen or heard or used the word at least once before, but only rarely; and so on until 9, which represents “VERY OFTEN,” that is, you have seen or heard or used the word nearly every day of your life.&lt;/p&gt;
+                &lt;p&gt;Do not be bothered if you are unable to give a definition of some of the words. Simply rate each one as to the number of times you have come in contact with it regardless of its meaning. There may be some words which you have used or heard more often than you have seen them. Or there may be other words which you have seen more often than you have used or heard them. In such cases, always give the word in the highest rating of the three. For example, you probably use or hear the word “cheers” often, but you may never have seen it in print. In this case, you would rate “cheers” as “OFTEN” and write down the number 6.&lt;/p&gt;
+                &lt;p&gt;Go to the list of words and begin rating them at your own speed. This is not a “speed” experiment, each participant will be given plenty of time to finish. On the other hand, do not spend too much time on each word. The important thing is for you to be as accurate as possible. Be as honest in your ratings as you can. Many of the words in this experiment are very rare, so you are not expected to have come in contact with all of them. Just make the best estimates you are capable of. &lt;/p&gt;
+                &lt;p&gt;If you do not know what a word means, please enter the letter X.&lt;/p&gt;
+              `,</t>
+  </si>
+  <si>
+    <t>This is an experiment to find out how often you have come in contact with certain words. You will be given a list of words and you are to rate each one as to the number of times that you experienced it by simply writing down a number according to a 1 to 9 scale. In this scale, 1 represents “NEVER,” that is, you have never seen or heard or used the word in your life; the number 2 represents “RARELY,” that is you have seen or heard or used the word at least once before, but only rarely; and so on until 9, which represents “VERY OFTEN,” that is, you have seen or heard or used the word nearly every day of your life.
+Do not be bothered if you are unable to give a definition of some of the words. Simply rate each one as to the number of times you have come in contact with it regardless of its meaning. There may be some words which you have used or heard more often than you have seen them. Or there may be other words which you have seen more often than you have used or heard them. In such cases, always give the word in the highest rating of the three. For example, you probably use or hear the word “cheers” often, but you may never have seen it in print. In this case, you would rate “cheers” as “OFTEN” and write down the number 6.
+Go to the list of words and begin rating them at your own speed. This is not a “speed” experiment, each participant will be given plenty of time to finish. On the other hand, do not spend too much time on each word. The important thing is for you to be as accurate as possible. Be as honest in your ratings as you can. Many of the words in this experiment are very rare, so you are not expected to have come in contact with all of them. Just make the best estimates you are capable of. 
+If you do not know what a word means, please enter the letter X.</t>
+  </si>
+  <si>
+    <t>187-200</t>
+  </si>
+  <si>
+    <t>title:
+                  "For each word, rate how unfamiliar (1) or familiar (9) based on how often you personally come into contact with each word.",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each word, rate how unfamiliar (1) or familiar (9) based on how often you personally come into contact with each word.
+               </t>
+  </si>
+  <si>
+    <t>227-228</t>
+  </si>
+  <si>
+    <t>277-282</t>
+  </si>
+  <si>
+    <t>arousal</t>
+  </si>
+  <si>
+    <t>&lt;title&gt;Arousal Study&lt;/title&gt;</t>
+  </si>
+  <si>
+    <t>Arousal Study</t>
+  </si>
+  <si>
+    <t>html: `
+                &lt;figure style="margin: 0 0 1rem 0;"&gt;
+                  &lt;img
+                    src="arousal_image.png"
+                    alt="Self-Assessment Manikin (SAM) scale for arousal"
+                    style="max-width: 100%; height: auto; display: block;"
+                  /&gt;
+                  &lt;figcaption style="font-size: 0.9em; margin-top: 0.25rem;"&gt;
+                    &lt;em&gt;Self-Assessment Manikin (SAM)&lt;/em&gt; arousal scale. Procedure adapted from Prete, Laeng, &amp;amp; Tommasi (2022); SAM from Bradley &amp;amp; Lang (1999).
+                   &lt;/figcaption&gt;
+                &lt;/figure&gt;
+                &lt;p&gt;The study being conducted today is investigating emotion, and how people respond to different types of words.&lt;/p&gt;
+                &lt;p&gt;We call this set of figures SAM, and you will be using these figures to rate how you felt while reading each word. SAM shows different kinds of feelings: Excited vs. Calm. You will use these scales to make all ratings for each word that you read. Please notice that each of the feelings are arrayed along a different scale. &lt;/p&gt;
+                &lt;p&gt;The excited or calm scale is the second type of feeling displayed here. At one extreme of this scale you are stimulated, excited, frenzied, jittery, wide-awake, or aroused.  When you feel completely aroused, select the 9 on the right. Now look at the other end of the excited-calm scale, which is the completely opposite feeling. Here you would feel completely relaxed, calm, sluggish, dull, sleepy, or unaroused. Indicate feeling calm by selecting the 1 on the left. The figures also allow you to describe intermediate feelings of excitedness or calmness by selecting any other number. If you are not excited nor at all calm, select the 4 in the middle. &lt;/p&gt;
+                &lt;p&gt;Please work at a rapid place and don’t spend too much time thinking about each word. Rather, make your ratings based on your first and immediate reaction as you read each word.&lt;/p&gt;
+              `</t>
+  </si>
+  <si>
+    <t>Self-Assessment Manikin (SAM) scale for arousal
+Self-Assessment Manikin (SAM) arousal scale. Procedure adapted from Prete, Laeng, &amp;amp; Tommasi (2022); SAM from Bradley &amp;amp; Lang (1999).
+The study being conducted today is investigating emotion, and how people respond to different types of words.
+We call this set of figures SAM, and you will be using these figures to rate how you felt while reading each word. SAM shows different kinds of feelings: Excited vs. Calm. You will use these scales to make all ratings for each word that you read. Please notice that each of the feelings are arrayed along a different scale.
+The excited or calm scale is the second type of feeling displayed here. At one extreme of this scale you are stimulated, excited, frenzied, jittery, wide-awake, or aroused.  When you feel completely aroused, select the 9 on the right. Now look at the other end of the excited-calm scale, which is the completely opposite feeling. Here you would feel completely relaxed, calm, sluggish, dull, sleepy, or unaroused. Indicate feeling calm by selecting the 1 on the left. The figures also allow you to describe intermediate feelings of excitedness or calmness by selecting any other number. If you are not excited nor at all calm, select the 4 in the middle.
+Please work at a rapid place and don’t spend too much time thinking about each word. Rather, make your ratings based on your first and immediate reaction as you read each word.</t>
+  </si>
+  <si>
+    <t>const sampleWords = [
+    "dog",
+    "bicycle",
+    "apple",
+    "school",
+    "mountain",
+    "telephone",
+    "democracy",
+    "hospital",
+    "garden",
+    "computer",
+    "river",
+    "window",
+  ]</t>
+  </si>
+  <si>
+    <t>const samHtml = `
+        &lt;figure style="margin: 0 0 1rem 0;"&gt;
+          &lt;img
+            src="arousal_image.png"
+            alt="Self-Assessment Manikin (SAM) scale for arousal"
+            style="max-width: 100%; height: auto; display: block;"
+          /&gt;
+          &lt;figcaption style="font-size: 0.9em; margin-top: 0.25rem;"&gt;
+            &lt;em&gt;Self-Assessment Manikin (SAM)&lt;/em&gt; arousal scale. Procedure adapted from Prete, Laeng, &amp;amp; Tommasi (2022); SAM from Bradley &amp;amp; Lang (1999).
+          &lt;/figcaption&gt;
+        &lt;/figure&gt;
+      `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-Assessment Manikin (SAM) scale for arousal
+Self-Assessment Manikin (SAM) arousal scale. Procedure adapted from Prete, Laeng, &amp;amp; Tommasi (2022); SAM from Bradley &amp;amp; Lang (1999).
+</t>
+  </si>
+  <si>
+    <t>Self-Assessment Manikin (SAM) scale for valence
+Self-Assessment Manikin (SAM) valence scale. Procedure adapted from Prete, Laeng, &amp;amp; Tommasi (2022); SAM from Bradley &amp;amp; Lang (1999).</t>
+  </si>
+  <si>
+    <t>title: `Arousal ratings (Block ${blockIndex + 1} of ${wordBlocks.length})`,</t>
+  </si>
+  <si>
+    <t>Arousal ratings (Block ${blockIndex + 1} of ${wordBlocks.length})</t>
+  </si>
+  <si>
+    <t>title:
+                "For each word, rate AROUSAL (1 = very calm/relaxed, 9 = very excited/activated). If you do not know the word, choose X.",</t>
+  </si>
+  <si>
+    <t>For each word, rate AROUSAL (1 = very calm/relaxed, 9 = very excited/activated). If you do not know the word, choose X.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -80,8 +656,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -97,6 +679,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Addie Clark" id="{F74B45F1-8B85-0440-B3AF-FE51C9556700}" userId="S::AClark2@my.harrisburgu.edu::0bfef028-7007-49f9-b706-ebe73ca4ed85" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,37 +1002,2747 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A5" dT="2026-02-18T21:17:12.21" personId="{F74B45F1-8B85-0440-B3AF-FE51C9556700}" id="{2987ABC4-BFFE-D241-A1E9-00D4B209872D}">
+    <text xml:space="preserve">don't forget text for buttons e.g.,         
+completeText: "Finish",
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73FEBD9C-26F5-844B-9B44-9CEC60061FCB}">
-  <dimension ref="A1:B3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73FEBD9C-26F5-844B-9B44-9CEC60061FCB}">
+  <dimension ref="A1:E194"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="76.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.5" customWidth="1"/>
+    <col min="1" max="1" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.1640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="76" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
+    <col min="5" max="5" width="2.33203125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="153" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="238" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="1">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="238" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D58" s="1">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60" s="1">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" s="1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62" s="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D64" s="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D76" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" s="1">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" s="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" s="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" s="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D83" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84" s="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D85" s="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D86" s="1">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="238" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="221" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D90" s="1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D91" s="1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D93" s="1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D94" s="1">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D96" s="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D97" s="1">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D98" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D99" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D109" s="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D110" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D111" s="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D112" s="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D113" s="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D115" s="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D116" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D117" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D118" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D119" s="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="170" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="238" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D122" s="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D123" s="1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D125" s="1">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D126" s="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D127" s="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D129" s="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D130" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D131" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D133" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D139" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D141" s="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D142" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D143" s="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D144" s="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D145" s="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D147" s="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D148" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D149" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D150" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D151" s="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="238" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D154" s="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D155" s="1">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D157" s="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D158" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D159" s="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D161" s="1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D162" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D163" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D165" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D166" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A167" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D167" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A168" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D168" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A171" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D171" s="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A172" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D172" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A173" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D173" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A174" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D174" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A175" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D175" s="1">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D176" s="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A177" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D177" s="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A178" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A179" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D179" s="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A180" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D180" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A181" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D181" s="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A182" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D182" s="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A183" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D183" s="1">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A184" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="238" x14ac:dyDescent="0.2">
+      <c r="A185" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="221" x14ac:dyDescent="0.2">
+      <c r="A186" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A187" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D187" s="1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A188" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D188" s="1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A189" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A190" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D190" s="1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A191" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D191" s="1">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A192" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A193" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D193" s="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A194" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D194" s="1">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/03-Tasks/translation_template.xlsx
+++ b/03-Tasks/translation_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/addieclark/Desktop/Harrisburg/SPAML/ML-One-Network/03-Tasks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erinbuchanan/GitHub/Research/2_projects/ManyLanguages-Grant/ML-One-Network/03-Tasks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21142FC-8269-FE4E-A72A-496398506125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62A4EAE-72B7-5944-96DC-DD499727FE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17180" yWindow="760" windowWidth="17520" windowHeight="21580" xr2:uid="{C0956B13-467A-1A4F-848B-48D89FEF3597}"/>
+    <workbookView xWindow="12720" yWindow="660" windowWidth="17520" windowHeight="18980" xr2:uid="{C0956B13-467A-1A4F-848B-48D89FEF3597}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={2987ABC4-BFFE-D241-A1E9-00D4B209872D}</author>
+    <author>tc={48DFFF22-2B7A-FB49-BCC1-31B109671D54}</author>
   </authors>
   <commentList>
     <comment ref="A5" authorId="0" shapeId="0" xr:uid="{2987ABC4-BFFE-D241-A1E9-00D4B209872D}">
@@ -49,6 +50,14 @@
     don't forget text for buttons e.g.,         
 completeText: "Finish",
 </t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="1" shapeId="0" xr:uid="{48DFFF22-2B7A-FB49-BCC1-31B109671D54}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    due the logic choices for consent and see other s</t>
       </text>
     </comment>
   </commentList>
@@ -621,7 +630,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -634,6 +643,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -683,6 +698,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Erin M. Buchanan" id="{432309A6-704F-F240-8FE6-B738A4647BFF}" userId="S::EBuchanan@HarrisburgU.edu::a202a620-6e05-42b1-a3fc-fcfad0b42cdc" providerId="AD"/>
   <person displayName="Addie Clark" id="{F74B45F1-8B85-0440-B3AF-FE51C9556700}" userId="S::AClark2@my.harrisburgu.edu::0bfef028-7007-49f9-b706-ebe73ca4ed85" providerId="AD"/>
 </personList>
 </file>
@@ -1009,12 +1025,15 @@
 completeText: "Finish",
 </text>
   </threadedComment>
+  <threadedComment ref="B12" dT="2026-02-25T21:48:16.38" personId="{432309A6-704F-F240-8FE6-B738A4647BFF}" id="{48DFFF22-2B7A-FB49-BCC1-31B109671D54}">
+    <text>due the logic choices for consent and see other s</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73FEBD9C-26F5-844B-9B44-9CEC60061FCB}">
-  <dimension ref="A1:E194"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" bestFit="1" customWidth="1"/>
